--- a/trunk/psse_validation/data/NETS-NYPS68Bus.raw.xlsx
+++ b/trunk/psse_validation/data/NETS-NYPS68Bus.raw.xlsx
@@ -16,21 +16,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="164">
+  <si>
+    <t>names</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>Vm</t>
+  </si>
+  <si>
+    <t>Va(rad)</t>
+  </si>
   <si>
     <t>Va(deg)</t>
   </si>
   <si>
-    <t>Va(rad)</t>
-  </si>
-  <si>
-    <t>Vm</t>
-  </si>
-  <si>
-    <t>names</t>
-  </si>
-  <si>
-    <t>number</t>
+    <t>Vnom</t>
   </si>
   <si>
     <t xml:space="preserve">1           </t>
@@ -237,10 +240,25 @@
     <t xml:space="preserve">68          </t>
   </si>
   <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Q</t>
+    <t>Pf</t>
+  </si>
+  <si>
+    <t>Qf</t>
+  </si>
+  <si>
+    <t>Pt</t>
+  </si>
+  <si>
+    <t>Qt</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>ckt</t>
   </si>
   <si>
     <t>7_23_1</t>
@@ -847,10 +865,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -866,1365 +884,1572 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>-8.95625033111294</v>
+      <c r="B2" t="s">
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>-0.156316056910753</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1.04499990807203</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
+      <c r="E2">
+        <v>-0.156316056910753</v>
       </c>
       <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>-8.95625033111294</v>
+      </c>
+      <c r="G2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>-0.983462654654266</v>
+      <c r="B3" t="s">
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>-0.0171646613941209</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>0.980000019626639</v>
       </c>
-      <c r="E3" t="s">
-        <v>6</v>
+      <c r="E3">
+        <v>-0.0171646613941209</v>
       </c>
       <c r="F3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>-0.983462654654266</v>
+      </c>
+      <c r="G3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>1.61290080232977</v>
+      <c r="B4" t="s">
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>0.0281504295087128</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>0.98299998551895</v>
       </c>
-      <c r="E4" t="s">
-        <v>7</v>
+      <c r="E4">
+        <v>0.0281504295087128</v>
       </c>
       <c r="F4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>1.61290080232977</v>
+      </c>
+      <c r="G4">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>1.66833965368764</v>
+      <c r="B5" t="s">
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>0.0291180199984314</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>0.996999950355692</v>
       </c>
-      <c r="E5" t="s">
-        <v>8</v>
+      <c r="E5">
+        <v>0.0291180199984314</v>
       </c>
       <c r="F5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>1.66833965368764</v>
+      </c>
+      <c r="G5">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>-0.627644476038168</v>
+      <c r="B6" t="s">
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>-0.0109544626388207</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>1.01100001918671</v>
       </c>
-      <c r="E6" t="s">
-        <v>9</v>
+      <c r="E6">
+        <v>-0.0109544626388207</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>-0.627644476038168</v>
+      </c>
+      <c r="G6">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7">
-        <v>3.84249707682429</v>
+      <c r="B7" t="s">
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>0.0670642254888413</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>1.04999996887778</v>
       </c>
-      <c r="E7" t="s">
-        <v>10</v>
+      <c r="E7">
+        <v>0.0670642254888413</v>
       </c>
       <c r="F7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>3.84249707682429</v>
+      </c>
+      <c r="G7">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8">
-        <v>6.0307418115887</v>
+      <c r="B8" t="s">
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>0.10525630094991</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>1.06299998022576</v>
       </c>
-      <c r="E8" t="s">
-        <v>11</v>
+      <c r="E8">
+        <v>0.10525630094991</v>
       </c>
       <c r="F8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>6.0307418115887</v>
+      </c>
+      <c r="G8">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9">
-        <v>-2.84097881566325</v>
+      <c r="B9" t="s">
+        <v>13</v>
       </c>
       <c r="C9">
-        <v>-0.0495844343127328</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>1.03000001586736</v>
       </c>
-      <c r="E9" t="s">
-        <v>12</v>
+      <c r="E9">
+        <v>-0.0495844343127328</v>
       </c>
       <c r="F9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>-2.84097881566325</v>
+      </c>
+      <c r="G9">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10">
-        <v>2.65236890875994</v>
+      <c r="B10" t="s">
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>0.0462925704353899</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>1.02500003186875</v>
       </c>
-      <c r="E10" t="s">
-        <v>13</v>
+      <c r="E10">
+        <v>0.0462925704353899</v>
       </c>
       <c r="F10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>2.65236890875994</v>
+      </c>
+      <c r="G10">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11">
-        <v>-9.64386046158838</v>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>-0.168317117657617</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>1.00999999819579</v>
       </c>
-      <c r="E11" t="s">
-        <v>14</v>
+      <c r="E11">
+        <v>-0.168317117657617</v>
       </c>
       <c r="F11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>-9.64386046158838</v>
+      </c>
+      <c r="G11">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12">
-        <v>-7.22448007089417</v>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>-0.126090963981817</v>
+        <v>11</v>
       </c>
       <c r="D12">
         <v>1.00000001753285</v>
       </c>
-      <c r="E12" t="s">
-        <v>15</v>
+      <c r="E12">
+        <v>-0.126090963981817</v>
       </c>
       <c r="F12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>-7.22448007089417</v>
+      </c>
+      <c r="G12">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13">
-        <v>-22.6313036061614</v>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>-0.394990761945982</v>
+        <v>12</v>
       </c>
       <c r="D13">
         <v>1.01559998858108</v>
       </c>
-      <c r="E13" t="s">
-        <v>16</v>
+      <c r="E13">
+        <v>-0.394990761945982</v>
       </c>
       <c r="F13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>-22.6313036061614</v>
+      </c>
+      <c r="G13">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14">
-        <v>-28.65388717939</v>
+      <c r="B14" t="s">
+        <v>18</v>
       </c>
       <c r="C14">
-        <v>-0.500104674775346</v>
+        <v>13</v>
       </c>
       <c r="D14">
         <v>1.01100005256325</v>
       </c>
-      <c r="E14" t="s">
-        <v>17</v>
+      <c r="E14">
+        <v>-0.500104674775346</v>
       </c>
       <c r="F14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>-28.65388717939</v>
+      </c>
+      <c r="G14">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15">
-        <v>10.9620075960388</v>
+      <c r="B15" t="s">
+        <v>19</v>
       </c>
       <c r="C15">
-        <v>0.191323125179505</v>
+        <v>14</v>
       </c>
       <c r="D15">
         <v>0.99999997643032</v>
       </c>
-      <c r="E15" t="s">
-        <v>18</v>
+      <c r="E15">
+        <v>0.191323125179505</v>
       </c>
       <c r="F15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>10.9620075960388</v>
+      </c>
+      <c r="G15">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16">
-        <v>0.0168285977907448</v>
+      <c r="B16" t="s">
+        <v>20</v>
       </c>
       <c r="C16">
-        <v>0.00029371443994234</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>0.99999998352944</v>
       </c>
-      <c r="E16" t="s">
-        <v>19</v>
+      <c r="E16">
+        <v>0.00029371443994234</v>
       </c>
       <c r="F16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>0.0168285977907448</v>
+      </c>
+      <c r="G16">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
         <v>0</v>
       </c>
-      <c r="C17">
+      <c r="F17">
         <v>0</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18">
-        <v>-36.0268775239328</v>
+      <c r="B18" t="s">
+        <v>22</v>
       </c>
       <c r="C18">
-        <v>-0.62878763200537</v>
+        <v>17</v>
       </c>
       <c r="D18">
         <v>0.949925628446443</v>
       </c>
-      <c r="E18" t="s">
-        <v>21</v>
+      <c r="E18">
+        <v>-0.62878763200537</v>
       </c>
       <c r="F18">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>-36.0268775239328</v>
+      </c>
+      <c r="G18">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19">
-        <v>-5.80540298165301</v>
+      <c r="B19" t="s">
+        <v>23</v>
       </c>
       <c r="C19">
-        <v>-0.101323396434941</v>
+        <v>18</v>
       </c>
       <c r="D19">
         <v>1.00233155681965</v>
       </c>
-      <c r="E19" t="s">
-        <v>22</v>
+      <c r="E19">
+        <v>-0.101323396434941</v>
       </c>
       <c r="F19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>-5.80540298165301</v>
+      </c>
+      <c r="G19">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20">
-        <v>-4.26335241862467</v>
+      <c r="B20" t="s">
+        <v>24</v>
       </c>
       <c r="C20">
-        <v>-0.074409536877864</v>
+        <v>19</v>
       </c>
       <c r="D20">
         <v>0.931976885123976</v>
       </c>
-      <c r="E20" t="s">
-        <v>23</v>
+      <c r="E20">
+        <v>-0.074409536877864</v>
       </c>
       <c r="F20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>-4.26335241862467</v>
+      </c>
+      <c r="G20">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21">
-        <v>-5.87443951649998</v>
+      <c r="B21" t="s">
+        <v>25</v>
       </c>
       <c r="C21">
-        <v>-0.102528311272188</v>
+        <v>20</v>
       </c>
       <c r="D21">
         <v>0.980613185384165</v>
       </c>
-      <c r="E21" t="s">
-        <v>24</v>
+      <c r="E21">
+        <v>-0.102528311272188</v>
       </c>
       <c r="F21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>-5.87443951649998</v>
+      </c>
+      <c r="G21">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22">
-        <v>-7.05389687367088</v>
+      <c r="B22" t="s">
+        <v>26</v>
       </c>
       <c r="C22">
-        <v>-0.123113725541691</v>
+        <v>21</v>
       </c>
       <c r="D22">
         <v>0.960244726146639</v>
       </c>
-      <c r="E22" t="s">
-        <v>25</v>
+      <c r="E22">
+        <v>-0.123113725541691</v>
       </c>
       <c r="F22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>-7.05389687367088</v>
+      </c>
+      <c r="G22">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23">
-        <v>-1.8009794701307</v>
+      <c r="B23" t="s">
+        <v>27</v>
       </c>
       <c r="C23">
-        <v>-0.0314330215146036</v>
+        <v>22</v>
       </c>
       <c r="D23">
         <v>0.993681143922307</v>
       </c>
-      <c r="E23" t="s">
-        <v>26</v>
+      <c r="E23">
+        <v>-0.0314330215146036</v>
       </c>
       <c r="F23">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>-1.8009794701307</v>
+      </c>
+      <c r="G23">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24">
-        <v>-2.16056653894548</v>
+      <c r="B24" t="s">
+        <v>28</v>
       </c>
       <c r="C24">
-        <v>-0.0377089998130169</v>
+        <v>23</v>
       </c>
       <c r="D24">
         <v>0.996110411494807</v>
       </c>
-      <c r="E24" t="s">
-        <v>27</v>
+      <c r="E24">
+        <v>-0.0377089998130169</v>
       </c>
       <c r="F24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>-2.16056653894548</v>
+      </c>
+      <c r="G24">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25">
-        <v>-9.87669553649337</v>
+      <c r="B25" t="s">
+        <v>29</v>
       </c>
       <c r="C25">
-        <v>-0.172380856328837</v>
+        <v>24</v>
       </c>
       <c r="D25">
         <v>0.958703924557947</v>
       </c>
-      <c r="E25" t="s">
-        <v>28</v>
+      <c r="E25">
+        <v>-0.172380856328837</v>
       </c>
       <c r="F25">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>-9.87669553649337</v>
+      </c>
+      <c r="G25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26">
-        <v>-9.99950888166389</v>
+      <c r="B26" t="s">
+        <v>30</v>
       </c>
       <c r="C26">
-        <v>-0.174524353567451</v>
+        <v>25</v>
       </c>
       <c r="D26">
         <v>0.998103759561368</v>
       </c>
-      <c r="E26" t="s">
-        <v>29</v>
+      <c r="E26">
+        <v>-0.174524353567451</v>
       </c>
       <c r="F26">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>-9.99950888166389</v>
+      </c>
+      <c r="G26">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27">
-        <v>-11.0194461967988</v>
+      <c r="B27" t="s">
+        <v>31</v>
       </c>
       <c r="C27">
-        <v>-0.192325617880505</v>
+        <v>26</v>
       </c>
       <c r="D27">
         <v>0.986860130958713</v>
       </c>
-      <c r="E27" t="s">
-        <v>30</v>
+      <c r="E27">
+        <v>-0.192325617880505</v>
       </c>
       <c r="F27">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>-11.0194461967988</v>
+      </c>
+      <c r="G27">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28">
-        <v>-12.8570953312675</v>
+      <c r="B28" t="s">
+        <v>32</v>
       </c>
       <c r="C28">
-        <v>-0.224398645773409</v>
+        <v>27</v>
       </c>
       <c r="D28">
         <v>0.967893759732871</v>
       </c>
-      <c r="E28" t="s">
-        <v>31</v>
+      <c r="E28">
+        <v>-0.224398645773409</v>
       </c>
       <c r="F28">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>-12.8570953312675</v>
+      </c>
+      <c r="G28">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29">
-        <v>-7.49675782207791</v>
+      <c r="B29" t="s">
+        <v>33</v>
       </c>
       <c r="C29">
-        <v>-0.130843107219899</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>0.989732689169461</v>
       </c>
-      <c r="E29" t="s">
-        <v>32</v>
+      <c r="E29">
+        <v>-0.130843107219899</v>
       </c>
       <c r="F29">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>-7.49675782207791</v>
+      </c>
+      <c r="G29">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30">
-        <v>-4.54644556087574</v>
+      <c r="B30" t="s">
+        <v>34</v>
       </c>
       <c r="C30">
-        <v>-0.0793504442999619</v>
+        <v>29</v>
       </c>
       <c r="D30">
         <v>0.992090436723662</v>
       </c>
-      <c r="E30" t="s">
-        <v>33</v>
+      <c r="E30">
+        <v>-0.0793504442999619</v>
       </c>
       <c r="F30">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>-4.54644556087574</v>
+      </c>
+      <c r="G30">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31">
-        <v>-19.7099841622257</v>
+      <c r="B31" t="s">
+        <v>35</v>
       </c>
       <c r="C31">
-        <v>-0.344004119146774</v>
+        <v>30</v>
       </c>
       <c r="D31">
         <v>0.976182693956642</v>
       </c>
-      <c r="E31" t="s">
-        <v>34</v>
+      <c r="E31">
+        <v>-0.344004119146774</v>
       </c>
       <c r="F31">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>-19.7099841622257</v>
+      </c>
+      <c r="G31">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32">
-        <v>-17.4640151245448</v>
+      <c r="B32" t="s">
+        <v>36</v>
       </c>
       <c r="C32">
-        <v>-0.304804564541394</v>
+        <v>31</v>
       </c>
       <c r="D32">
         <v>0.983811509591688</v>
       </c>
-      <c r="E32" t="s">
-        <v>35</v>
+      <c r="E32">
+        <v>-0.304804564541394</v>
       </c>
       <c r="F32">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>-17.4640151245448</v>
+      </c>
+      <c r="G32">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33">
-        <v>-15.2375095279917</v>
+      <c r="B33" t="s">
+        <v>37</v>
       </c>
       <c r="C33">
-        <v>-0.265944711067463</v>
+        <v>32</v>
       </c>
       <c r="D33">
         <v>0.969882825521298</v>
       </c>
-      <c r="E33" t="s">
-        <v>36</v>
+      <c r="E33">
+        <v>-0.265944711067463</v>
       </c>
       <c r="F33">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>-15.2375095279917</v>
+      </c>
+      <c r="G33">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34">
-        <v>-19.7580376323341</v>
+      <c r="B34" t="s">
+        <v>38</v>
       </c>
       <c r="C34">
-        <v>-0.344842810417174</v>
+        <v>33</v>
       </c>
       <c r="D34">
         <v>0.973809153432061</v>
       </c>
-      <c r="E34" t="s">
-        <v>37</v>
+      <c r="E34">
+        <v>-0.344842810417174</v>
       </c>
       <c r="F34">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>-19.7580376323341</v>
+      </c>
+      <c r="G34">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35">
-        <v>-26.115878843704</v>
+      <c r="B35" t="s">
+        <v>39</v>
       </c>
       <c r="C35">
-        <v>-0.455808072874565</v>
+        <v>34</v>
       </c>
       <c r="D35">
         <v>0.980033299770081</v>
       </c>
-      <c r="E35" t="s">
-        <v>38</v>
+      <c r="E35">
+        <v>-0.455808072874565</v>
       </c>
       <c r="F35">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>-26.115878843704</v>
+      </c>
+      <c r="G35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36">
-        <v>-27.0885726653743</v>
+      <c r="B36" t="s">
+        <v>40</v>
       </c>
       <c r="C36">
-        <v>-0.472784782676518</v>
+        <v>35</v>
       </c>
       <c r="D36">
         <v>1.04302439390652</v>
       </c>
-      <c r="E36" t="s">
-        <v>39</v>
+      <c r="E36">
+        <v>-0.472784782676518</v>
       </c>
       <c r="F36">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>-27.0885726653743</v>
+      </c>
+      <c r="G36">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37">
-        <v>-28.8273391712612</v>
+      <c r="B37" t="s">
+        <v>41</v>
       </c>
       <c r="C37">
-        <v>-0.503131983127641</v>
+        <v>36</v>
       </c>
       <c r="D37">
         <v>0.960641236303475</v>
       </c>
-      <c r="E37" t="s">
-        <v>40</v>
+      <c r="E37">
+        <v>-0.503131983127641</v>
       </c>
       <c r="F37">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>-28.8273391712612</v>
+      </c>
+      <c r="G37">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38">
-        <v>-11.7880422398489</v>
+      <c r="B38" t="s">
+        <v>42</v>
       </c>
       <c r="C38">
-        <v>-0.205740149449531</v>
+        <v>37</v>
       </c>
       <c r="D38">
         <v>0.955511955825814</v>
       </c>
-      <c r="E38" t="s">
-        <v>41</v>
+      <c r="E38">
+        <v>-0.205740149449531</v>
       </c>
       <c r="F38">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>-11.7880422398489</v>
+      </c>
+      <c r="G38">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39">
-        <v>-18.7593473259653</v>
+      <c r="B39" t="s">
+        <v>43</v>
       </c>
       <c r="C39">
-        <v>-0.327412376363288</v>
+        <v>38</v>
       </c>
       <c r="D39">
         <v>0.988975977303589</v>
       </c>
-      <c r="E39" t="s">
-        <v>42</v>
+      <c r="E39">
+        <v>-0.327412376363288</v>
       </c>
       <c r="F39">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>-18.7593473259653</v>
+      </c>
+      <c r="G39">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B40">
-        <v>-39.2901583420896</v>
+      <c r="B40" t="s">
+        <v>44</v>
       </c>
       <c r="C40">
-        <v>-0.68574262669938</v>
+        <v>39</v>
       </c>
       <c r="D40">
         <v>0.991543173057476</v>
       </c>
-      <c r="E40" t="s">
-        <v>43</v>
+      <c r="E40">
+        <v>-0.68574262669938</v>
       </c>
       <c r="F40">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>-39.2901583420896</v>
+      </c>
+      <c r="G40">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="B41">
-        <v>-13.6400198745728</v>
+      <c r="B41" t="s">
+        <v>45</v>
       </c>
       <c r="C41">
-        <v>-0.23806325684876</v>
+        <v>40</v>
       </c>
       <c r="D41">
         <v>1.04422129971906</v>
       </c>
-      <c r="E41" t="s">
-        <v>44</v>
+      <c r="E41">
+        <v>-0.23806325684876</v>
       </c>
       <c r="F41">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>-13.6400198745728</v>
+      </c>
+      <c r="G41">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="B42">
-        <v>9.42718649577138</v>
+      <c r="B42" t="s">
+        <v>46</v>
       </c>
       <c r="C42">
-        <v>0.164535443550757</v>
+        <v>41</v>
       </c>
       <c r="D42">
         <v>0.999646405959075</v>
       </c>
-      <c r="E42" t="s">
-        <v>45</v>
+      <c r="E42">
+        <v>0.164535443550757</v>
       </c>
       <c r="F42">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>9.42718649577138</v>
+      </c>
+      <c r="G42">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="B43">
-        <v>-0.843533694806371</v>
+      <c r="B43" t="s">
+        <v>47</v>
       </c>
       <c r="C43">
-        <v>-0.0147224403258842</v>
+        <v>42</v>
       </c>
       <c r="D43">
         <v>0.998961705696919</v>
       </c>
-      <c r="E43" t="s">
-        <v>46</v>
+      <c r="E43">
+        <v>-0.0147224403258842</v>
       </c>
       <c r="F43">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>-0.843533694806371</v>
+      </c>
+      <c r="G43">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="B44">
-        <v>-37.9087733127378</v>
+      <c r="B44" t="s">
+        <v>48</v>
       </c>
       <c r="C44">
-        <v>-0.661632909699432</v>
+        <v>43</v>
       </c>
       <c r="D44">
         <v>0.976497576662699</v>
       </c>
-      <c r="E44" t="s">
-        <v>47</v>
+      <c r="E44">
+        <v>-0.661632909699432</v>
       </c>
       <c r="F44">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>-37.9087733127378</v>
+      </c>
+      <c r="G44">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B45">
-        <v>-37.9863483240905</v>
+      <c r="B45" t="s">
+        <v>49</v>
       </c>
       <c r="C45">
-        <v>-0.662986849064809</v>
+        <v>44</v>
       </c>
       <c r="D45">
         <v>0.97748889362835</v>
       </c>
-      <c r="E45" t="s">
-        <v>48</v>
+      <c r="E45">
+        <v>-0.662986849064809</v>
       </c>
       <c r="F45">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>-37.9863483240905</v>
+      </c>
+      <c r="G45">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="B46">
-        <v>-29.3626441503682</v>
+      <c r="B46" t="s">
+        <v>50</v>
       </c>
       <c r="C46">
-        <v>-0.512474817515378</v>
+        <v>45</v>
       </c>
       <c r="D46">
         <v>1.04708961685155</v>
       </c>
-      <c r="E46" t="s">
-        <v>49</v>
+      <c r="E46">
+        <v>-0.512474817515378</v>
       </c>
       <c r="F46">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>-29.3626441503682</v>
+      </c>
+      <c r="G46">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="1">
         <v>45</v>
       </c>
-      <c r="B47">
-        <v>-20.5313992862993</v>
+      <c r="B47" t="s">
+        <v>51</v>
       </c>
       <c r="C47">
-        <v>-0.358340517587537</v>
+        <v>46</v>
       </c>
       <c r="D47">
         <v>0.990316895493555</v>
       </c>
-      <c r="E47" t="s">
-        <v>50</v>
+      <c r="E47">
+        <v>-0.358340517587537</v>
       </c>
       <c r="F47">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>-20.5313992862993</v>
+      </c>
+      <c r="G47">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="B48">
-        <v>-19.497595852348</v>
+      <c r="B48" t="s">
+        <v>52</v>
       </c>
       <c r="C48">
-        <v>-0.340297243846663</v>
+        <v>47</v>
       </c>
       <c r="D48">
         <v>1.01840117818214</v>
       </c>
-      <c r="E48" t="s">
-        <v>51</v>
+      <c r="E48">
+        <v>-0.340297243846663</v>
       </c>
       <c r="F48">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>-19.497595852348</v>
+      </c>
+      <c r="G48">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="1">
         <v>47</v>
       </c>
-      <c r="B49">
-        <v>-18.3761079445094</v>
+      <c r="B49" t="s">
+        <v>53</v>
       </c>
       <c r="C49">
-        <v>-0.320723587333577</v>
+        <v>48</v>
       </c>
       <c r="D49">
         <v>1.03374470911574</v>
       </c>
-      <c r="E49" t="s">
-        <v>52</v>
+      <c r="E49">
+        <v>-0.320723587333577</v>
       </c>
       <c r="F49">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>-18.3761079445094</v>
+      </c>
+      <c r="G49">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="1">
         <v>48</v>
       </c>
-      <c r="B50">
-        <v>-19.8196218193865</v>
+      <c r="B50" t="s">
+        <v>54</v>
       </c>
       <c r="C50">
-        <v>-0.345917657248403</v>
+        <v>49</v>
       </c>
       <c r="D50">
         <v>0.993614580732536</v>
       </c>
-      <c r="E50" t="s">
-        <v>53</v>
+      <c r="E50">
+        <v>-0.345917657248403</v>
       </c>
       <c r="F50">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>-19.8196218193865</v>
+      </c>
+      <c r="G50">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="1">
         <v>49</v>
       </c>
-      <c r="B51">
-        <v>-19.0520956286636</v>
+      <c r="B51" t="s">
+        <v>55</v>
       </c>
       <c r="C51">
-        <v>-0.332521798124999</v>
+        <v>50</v>
       </c>
       <c r="D51">
         <v>1.06024452854093</v>
       </c>
-      <c r="E51" t="s">
-        <v>54</v>
+      <c r="E51">
+        <v>-0.332521798124999</v>
       </c>
       <c r="F51">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>-19.0520956286636</v>
+      </c>
+      <c r="G51">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="1">
         <v>50</v>
       </c>
-      <c r="B52">
-        <v>-27.2881628420392</v>
+      <c r="B52" t="s">
+        <v>56</v>
       </c>
       <c r="C52">
-        <v>-0.476268288413958</v>
+        <v>51</v>
       </c>
       <c r="D52">
         <v>1.06337459325806</v>
       </c>
-      <c r="E52" t="s">
-        <v>55</v>
+      <c r="E52">
+        <v>-0.476268288413958</v>
       </c>
       <c r="F52">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>-27.2881628420392</v>
+      </c>
+      <c r="G52">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" s="1">
         <v>51</v>
       </c>
-      <c r="B53">
-        <v>-12.8334418450454</v>
+      <c r="B53" t="s">
+        <v>57</v>
       </c>
       <c r="C53">
-        <v>-0.223985814559259</v>
+        <v>52</v>
       </c>
       <c r="D53">
         <v>0.954537922364184</v>
       </c>
-      <c r="E53" t="s">
-        <v>56</v>
+      <c r="E53">
+        <v>-0.223985814559259</v>
       </c>
       <c r="F53">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>-12.8334418450454</v>
+      </c>
+      <c r="G53">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="1">
         <v>52</v>
       </c>
-      <c r="B54">
-        <v>-18.9372647396677</v>
+      <c r="B54" t="s">
+        <v>58</v>
       </c>
       <c r="C54">
-        <v>-0.330517621029027</v>
+        <v>53</v>
       </c>
       <c r="D54">
         <v>0.98633615044796</v>
       </c>
-      <c r="E54" t="s">
-        <v>57</v>
+      <c r="E54">
+        <v>-0.330517621029027</v>
       </c>
       <c r="F54">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>-18.9372647396677</v>
+      </c>
+      <c r="G54">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" s="1">
         <v>53</v>
       </c>
-      <c r="B55">
-        <v>-11.5369927123579</v>
+      <c r="B55" t="s">
+        <v>59</v>
       </c>
       <c r="C55">
-        <v>-0.201358508609236</v>
+        <v>54</v>
       </c>
       <c r="D55">
         <v>0.985714264311474</v>
       </c>
-      <c r="E55" t="s">
-        <v>58</v>
+      <c r="E55">
+        <v>-0.201358508609236</v>
       </c>
       <c r="F55">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+        <v>-11.5369927123579</v>
+      </c>
+      <c r="G55">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" s="1">
         <v>54</v>
       </c>
-      <c r="B56">
-        <v>-13.2178786281454</v>
+      <c r="B56" t="s">
+        <v>60</v>
       </c>
       <c r="C56">
-        <v>-0.230695502190129</v>
+        <v>55</v>
       </c>
       <c r="D56">
         <v>0.95711901486687</v>
       </c>
-      <c r="E56" t="s">
-        <v>59</v>
+      <c r="E56">
+        <v>-0.230695502190129</v>
       </c>
       <c r="F56">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+        <v>-13.2178786281454</v>
+      </c>
+      <c r="G56">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="1">
         <v>55</v>
       </c>
-      <c r="B57">
-        <v>-11.9592630026319</v>
+      <c r="B57" t="s">
+        <v>61</v>
       </c>
       <c r="C57">
-        <v>-0.20872851550787</v>
+        <v>56</v>
       </c>
       <c r="D57">
         <v>0.920844878776412</v>
       </c>
-      <c r="E57" t="s">
-        <v>60</v>
+      <c r="E57">
+        <v>-0.20872851550787</v>
       </c>
       <c r="F57">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>-11.9592630026319</v>
+      </c>
+      <c r="G57">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" s="1">
         <v>56</v>
       </c>
-      <c r="B58">
-        <v>-11.2128744424914</v>
+      <c r="B58" t="s">
+        <v>62</v>
       </c>
       <c r="C58">
-        <v>-0.195701577634199</v>
+        <v>57</v>
       </c>
       <c r="D58">
         <v>0.910195168060924</v>
       </c>
-      <c r="E58" t="s">
-        <v>61</v>
+      <c r="E58">
+        <v>-0.195701577634199</v>
       </c>
       <c r="F58">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+        <v>-11.2128744424914</v>
+      </c>
+      <c r="G58">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" s="1">
         <v>57</v>
       </c>
-      <c r="B59">
-        <v>-10.4022504691269</v>
+      <c r="B59" t="s">
+        <v>63</v>
       </c>
       <c r="C59">
-        <v>-0.18155352030339</v>
+        <v>58</v>
       </c>
       <c r="D59">
         <v>0.909033021882754</v>
       </c>
-      <c r="E59" t="s">
-        <v>62</v>
+      <c r="E59">
+        <v>-0.18155352030339</v>
       </c>
       <c r="F59">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+        <v>-10.4022504691269</v>
+      </c>
+      <c r="G59">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" s="1">
         <v>58</v>
       </c>
-      <c r="B60">
-        <v>-13.3109638093067</v>
+      <c r="B60" t="s">
+        <v>64</v>
       </c>
       <c r="C60">
-        <v>-0.232320145086209</v>
+        <v>59</v>
       </c>
       <c r="D60">
         <v>0.903747162606715</v>
       </c>
-      <c r="E60" t="s">
-        <v>63</v>
+      <c r="E60">
+        <v>-0.232320145086209</v>
       </c>
       <c r="F60">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+        <v>-13.3109638093067</v>
+      </c>
+      <c r="G60">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" s="1">
         <v>59</v>
       </c>
-      <c r="B61">
-        <v>-14.0367946355693</v>
+      <c r="B61" t="s">
+        <v>65</v>
       </c>
       <c r="C61">
-        <v>-0.244988282816962</v>
+        <v>60</v>
       </c>
       <c r="D61">
         <v>0.906174577954914</v>
       </c>
-      <c r="E61" t="s">
-        <v>64</v>
+      <c r="E61">
+        <v>-0.244988282816962</v>
       </c>
       <c r="F61">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+        <v>-14.0367946355693</v>
+      </c>
+      <c r="G61">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" s="1">
         <v>60</v>
       </c>
-      <c r="B62">
-        <v>-23.2222392385419</v>
+      <c r="B62" t="s">
+        <v>66</v>
       </c>
       <c r="C62">
-        <v>-0.405304534398376</v>
+        <v>61</v>
       </c>
       <c r="D62">
         <v>0.955649492917269</v>
       </c>
-      <c r="E62" t="s">
-        <v>65</v>
+      <c r="E62">
+        <v>-0.405304534398376</v>
       </c>
       <c r="F62">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+        <v>-23.2222392385419</v>
+      </c>
+      <c r="G62">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" s="1">
         <v>61</v>
       </c>
-      <c r="B63">
-        <v>-7.31169356166919</v>
+      <c r="B63" t="s">
+        <v>67</v>
       </c>
       <c r="C63">
-        <v>-0.127613126547999</v>
+        <v>62</v>
       </c>
       <c r="D63">
         <v>0.91214811792737</v>
       </c>
-      <c r="E63" t="s">
-        <v>66</v>
+      <c r="E63">
+        <v>-0.127613126547999</v>
       </c>
       <c r="F63">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+        <v>-7.31169356166919</v>
+      </c>
+      <c r="G63">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" s="1">
         <v>62</v>
       </c>
-      <c r="B64">
-        <v>-8.36995280130316</v>
+      <c r="B64" t="s">
+        <v>68</v>
       </c>
       <c r="C64">
-        <v>-0.146083234619263</v>
+        <v>63</v>
       </c>
       <c r="D64">
         <v>0.909646779053913</v>
       </c>
-      <c r="E64" t="s">
-        <v>67</v>
+      <c r="E64">
+        <v>-0.146083234619263</v>
       </c>
       <c r="F64">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+        <v>-8.36995280130316</v>
+      </c>
+      <c r="G64">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" s="1">
         <v>63</v>
       </c>
-      <c r="B65">
-        <v>-8.37701496050509</v>
+      <c r="B65" t="s">
+        <v>69</v>
       </c>
       <c r="C65">
-        <v>-0.146206492549637</v>
+        <v>64</v>
       </c>
       <c r="D65">
         <v>0.836660142459983</v>
       </c>
-      <c r="E65" t="s">
-        <v>68</v>
+      <c r="E65">
+        <v>-0.146206492549637</v>
       </c>
       <c r="F65">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+        <v>-8.37701496050509</v>
+      </c>
+      <c r="G65">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" s="1">
         <v>64</v>
       </c>
-      <c r="B66">
-        <v>-8.18467410321315</v>
+      <c r="B66" t="s">
+        <v>70</v>
       </c>
       <c r="C66">
-        <v>-0.142849511303784</v>
+        <v>65</v>
       </c>
       <c r="D66">
         <v>0.912758738560206</v>
       </c>
-      <c r="E66" t="s">
-        <v>69</v>
+      <c r="E66">
+        <v>-0.142849511303784</v>
       </c>
       <c r="F66">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+        <v>-8.18467410321315</v>
+      </c>
+      <c r="G66">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" s="1">
         <v>65</v>
       </c>
-      <c r="B67">
-        <v>-10.1909303504105</v>
+      <c r="B67" t="s">
+        <v>71</v>
       </c>
       <c r="C67">
-        <v>-0.177865288456083</v>
+        <v>66</v>
       </c>
       <c r="D67">
         <v>0.919396349605661</v>
       </c>
-      <c r="E67" t="s">
-        <v>70</v>
+      <c r="E67">
+        <v>-0.177865288456083</v>
       </c>
       <c r="F67">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+        <v>-10.1909303504105</v>
+      </c>
+      <c r="G67">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" s="1">
         <v>66</v>
       </c>
-      <c r="B68">
-        <v>-11.4298512419154</v>
+      <c r="B68" t="s">
+        <v>72</v>
       </c>
       <c r="C68">
-        <v>-0.199488537184586</v>
+        <v>67</v>
       </c>
       <c r="D68">
         <v>0.928034667321407</v>
       </c>
-      <c r="E68" t="s">
-        <v>71</v>
+      <c r="E68">
+        <v>-0.199488537184586</v>
       </c>
       <c r="F68">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+        <v>-11.4298512419154</v>
+      </c>
+      <c r="G68">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" s="1">
         <v>67</v>
       </c>
-      <c r="B69">
-        <v>-10.0712276575527</v>
+      <c r="B69" t="s">
+        <v>73</v>
       </c>
       <c r="C69">
-        <v>-0.175776082342211</v>
+        <v>68</v>
       </c>
       <c r="D69">
         <v>0.948289271991008</v>
       </c>
-      <c r="E69" t="s">
-        <v>72</v>
+      <c r="E69">
+        <v>-0.175776082342211</v>
       </c>
       <c r="F69">
-        <v>68</v>
+        <v>-10.0712276575527</v>
+      </c>
+      <c r="G69">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2234,914 +2459,1889 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>75</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2">
         <v>560</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>290.831970214844</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>-558.238078713417</v>
+      </c>
+      <c r="F2">
+        <v>-194.983459472656</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>23</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3">
         <v>-2517.70922851562</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>198.989685058594</v>
       </c>
-      <c r="D3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>2553.08546066284</v>
+      </c>
+      <c r="F3">
+        <v>119.396392822266</v>
+      </c>
+      <c r="G3">
+        <v>17</v>
+      </c>
+      <c r="H3">
+        <v>36</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4">
         <v>108.709075927734</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>-91.6109313964844</v>
       </c>
-      <c r="D4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>-108.597090370953</v>
+      </c>
+      <c r="F4">
+        <v>97.7925333976746</v>
+      </c>
+      <c r="G4">
+        <v>17</v>
+      </c>
+      <c r="H4">
+        <v>43</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5">
         <v>-142.91325378418</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>-91.6142349243164</v>
       </c>
-      <c r="D5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>143.744677484035</v>
+      </c>
+      <c r="F5">
+        <v>104.085589408875</v>
+      </c>
+      <c r="G5">
+        <v>18</v>
+      </c>
+      <c r="H5">
+        <v>42</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6">
         <v>212.670715332031</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>-38.7987747192383</v>
       </c>
-      <c r="D6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>-209.220615625381</v>
+      </c>
+      <c r="F6">
+        <v>90.5956687927246</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>49</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7">
         <v>839.774108886719</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-241.845626831055</v>
       </c>
-      <c r="D7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7">
+        <v>-831.122114181519</v>
+      </c>
+      <c r="F7">
+        <v>449.493469238281</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>50</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8">
         <v>451.104400634766</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>-104.914260864258</v>
       </c>
-      <c r="D8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8">
+        <v>-447.200906991959</v>
+      </c>
+      <c r="F8">
+        <v>152.488090515137</v>
+      </c>
+      <c r="G8">
+        <v>19</v>
+      </c>
+      <c r="H8">
+        <v>68</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9">
         <v>-633.380554199219</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>-176.345520019531</v>
       </c>
-      <c r="D9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9">
+        <v>637.096001625061</v>
+      </c>
+      <c r="F9">
+        <v>241.365852355957</v>
+      </c>
+      <c r="G9">
+        <v>21</v>
+      </c>
+      <c r="H9">
+        <v>22</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10">
         <v>359.380584716797</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>61.3455276489258</v>
       </c>
-      <c r="D10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10">
+        <v>-358.213671565056</v>
+      </c>
+      <c r="F10">
+        <v>-41.6538677215576</v>
+      </c>
+      <c r="G10">
+        <v>21</v>
+      </c>
+      <c r="H10">
+        <v>68</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11">
         <v>62.9039764404297</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>-37.9871444702148</v>
       </c>
-      <c r="D11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11">
+        <v>-62.8748662061989</v>
+      </c>
+      <c r="F11">
+        <v>38.452908217907</v>
+      </c>
+      <c r="G11">
+        <v>22</v>
+      </c>
+      <c r="H11">
+        <v>23</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12">
         <v>373.112945556641</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>89.8026123046875</v>
       </c>
-      <c r="D12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12">
+        <v>-369.769048690796</v>
+      </c>
+      <c r="F12">
+        <v>-36.6042518615723</v>
+      </c>
+      <c r="G12">
+        <v>23</v>
+      </c>
+      <c r="H12">
+        <v>24</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13">
         <v>60.7690467834473</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>163.104095458984</v>
       </c>
-      <c r="D13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13">
+        <v>-60.6668015345931</v>
+      </c>
+      <c r="F13">
+        <v>-161.093272209167</v>
+      </c>
+      <c r="G13">
+        <v>24</v>
+      </c>
+      <c r="H13">
+        <v>68</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14">
         <v>57.2105484008789</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>3.10973834991455</v>
       </c>
-      <c r="D14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14">
+        <v>-57.0773464292288</v>
+      </c>
+      <c r="F14">
+        <v>-1.76523101329803</v>
+      </c>
+      <c r="G14">
+        <v>25</v>
+      </c>
+      <c r="H14">
+        <v>26</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15">
         <v>257.042510986328</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-68.5840148925781</v>
       </c>
-      <c r="D15" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15">
+        <v>-252.135821819305</v>
+      </c>
+      <c r="F15">
+        <v>74.6122326850891</v>
+      </c>
+      <c r="G15">
+        <v>25</v>
+      </c>
+      <c r="H15">
+        <v>54</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16">
         <v>218.828125</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>98.1616058349609</v>
       </c>
-      <c r="D16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16">
+        <v>-217.966352939606</v>
+      </c>
+      <c r="F16">
+        <v>-89.1129989624023</v>
+      </c>
+      <c r="G16">
+        <v>26</v>
+      </c>
+      <c r="H16">
+        <v>27</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17">
         <v>-125.765823364258</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>-28.6696434020996</v>
       </c>
-      <c r="D17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17">
+        <v>126.468025267124</v>
+      </c>
+      <c r="F17">
+        <v>36.4101943969727</v>
+      </c>
+      <c r="G17">
+        <v>26</v>
+      </c>
+      <c r="H17">
+        <v>28</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18">
         <v>-174.984954833984</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>-32.4204597473145</v>
       </c>
-      <c r="D18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18">
+        <v>176.795374393463</v>
+      </c>
+      <c r="F18">
+        <v>52.2715530395508</v>
+      </c>
+      <c r="G18">
+        <v>26</v>
+      </c>
+      <c r="H18">
+        <v>29</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19">
         <v>-93.9341354370117</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>62.1981315612793</v>
       </c>
-      <c r="D19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19">
+        <v>94.1394152343273</v>
+      </c>
+      <c r="F19">
+        <v>-59.466331243515</v>
+      </c>
+      <c r="G19">
+        <v>27</v>
+      </c>
+      <c r="H19">
+        <v>37</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20">
         <v>30.9004993438721</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>-26.1948146820068</v>
       </c>
-      <c r="D20" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20">
+        <v>-30.5576532483101</v>
+      </c>
+      <c r="F20">
+        <v>29.6232752799988</v>
+      </c>
+      <c r="G20">
+        <v>27</v>
+      </c>
+      <c r="H20">
+        <v>53</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21">
         <v>-332.468017578125</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>11.7944231033325</v>
       </c>
-      <c r="D21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21">
+        <v>334.056005954742</v>
+      </c>
+      <c r="F21">
+        <v>5.33316707611084</v>
+      </c>
+      <c r="G21">
+        <v>28</v>
+      </c>
+      <c r="H21">
+        <v>29</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22">
         <v>-202.780731201172</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>-37.6481056213379</v>
       </c>
-      <c r="D22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22">
+        <v>203.348166882992</v>
+      </c>
+      <c r="F22">
+        <v>45.8104496002197</v>
+      </c>
+      <c r="G22">
+        <v>30</v>
+      </c>
+      <c r="H22">
+        <v>31</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23">
         <v>-251.99153137207</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>29.1119041442871</v>
       </c>
-      <c r="D23" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23">
+        <v>253.659854888916</v>
+      </c>
+      <c r="F23">
+        <v>-9.09202194213867</v>
+      </c>
+      <c r="G23">
+        <v>30</v>
+      </c>
+      <c r="H23">
+        <v>32</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24">
         <v>-187.632385253906</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>-135.343032836914</v>
       </c>
-      <c r="D24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24">
+        <v>188.034143000841</v>
+      </c>
+      <c r="F24">
+        <v>139.059292316437</v>
+      </c>
+      <c r="G24">
+        <v>30</v>
+      </c>
+      <c r="H24">
+        <v>53</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25">
         <v>642.404602050781</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>143.879241943359</v>
       </c>
-      <c r="D25" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25">
+        <v>-637.997199058533</v>
+      </c>
+      <c r="F25">
+        <v>-101.428993225098</v>
+      </c>
+      <c r="G25">
+        <v>30</v>
+      </c>
+      <c r="H25">
+        <v>61</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26">
         <v>146.345001220703</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>-55.7766189575195</v>
       </c>
-      <c r="D26" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26">
+        <v>-146.0797727108</v>
+      </c>
+      <c r="F26">
+        <v>59.3210368156433</v>
+      </c>
+      <c r="G26">
+        <v>31</v>
+      </c>
+      <c r="H26">
+        <v>38</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27">
         <v>150.306838989258</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>-40.1224327087402</v>
       </c>
-      <c r="D27" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27">
+        <v>-149.920388489962</v>
+      </c>
+      <c r="F27">
+        <v>44.0593974590302</v>
+      </c>
+      <c r="G27">
+        <v>31</v>
+      </c>
+      <c r="H27">
+        <v>53</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28">
         <v>746.340148925781</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>-76.9993667602539</v>
       </c>
-      <c r="D28" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28">
+        <v>-741.562307834625</v>
+      </c>
+      <c r="F28">
+        <v>136.125152587891</v>
+      </c>
+      <c r="G28">
+        <v>32</v>
+      </c>
+      <c r="H28">
+        <v>33</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29">
         <v>669.774536132812</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>-57.7241058349609</v>
       </c>
-      <c r="D29" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29">
+        <v>-664.544067382812</v>
+      </c>
+      <c r="F29">
+        <v>132.377166748047</v>
+      </c>
+      <c r="G29">
+        <v>33</v>
+      </c>
+      <c r="H29">
+        <v>34</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30">
         <v>-40.2122421264648</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>-62.5336418151855</v>
       </c>
-      <c r="D30" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30">
+        <v>40.3070581778884</v>
+      </c>
+      <c r="F30">
+        <v>63.7030396461487</v>
+      </c>
+      <c r="G30">
+        <v>33</v>
+      </c>
+      <c r="H30">
+        <v>38</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31">
         <v>418.012298583984</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>-13.1970462799072</v>
       </c>
-      <c r="D31" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31">
+        <v>-411.899282932281</v>
+      </c>
+      <c r="F31">
+        <v>33.7590084075928</v>
+      </c>
+      <c r="G31">
+        <v>34</v>
+      </c>
+      <c r="H31">
+        <v>36</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32">
         <v>246.465850830078</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>-104.782012939453</v>
       </c>
-      <c r="D32" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32">
+        <v>-246.069513559341</v>
+      </c>
+      <c r="F32">
+        <v>114.690445899963</v>
+      </c>
+      <c r="G32">
+        <v>35</v>
+      </c>
+      <c r="H32">
+        <v>45</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33">
         <v>-893.186096191406</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>162.600357055664</v>
       </c>
-      <c r="D33" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33">
+        <v>903.144024848938</v>
+      </c>
+      <c r="F33">
+        <v>-73.8842697143555</v>
+      </c>
+      <c r="G33">
+        <v>36</v>
+      </c>
+      <c r="H33">
+        <v>61</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34">
         <v>202.582794189453</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>-10.1137247085571</v>
       </c>
-      <c r="D34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34">
+        <v>-202.26801353693</v>
+      </c>
+      <c r="F34">
+        <v>13.8011553287506</v>
+      </c>
+      <c r="G34">
+        <v>37</v>
+      </c>
+      <c r="H34">
+        <v>52</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35">
         <v>-296.722198486328</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>99.3251953125</v>
       </c>
-      <c r="D35" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35">
+        <v>297.482489943504</v>
+      </c>
+      <c r="F35">
+        <v>-89.6586322784424</v>
+      </c>
+      <c r="G35">
+        <v>37</v>
+      </c>
+      <c r="H35">
+        <v>68</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36">
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36">
         <v>105.772720336914</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>-32.2424964904785</v>
       </c>
-      <c r="D36" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36">
+        <v>-105.518240809441</v>
+      </c>
+      <c r="F36">
+        <v>35.5275959968567</v>
+      </c>
+      <c r="G36">
+        <v>38</v>
+      </c>
+      <c r="H36">
+        <v>46</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="s">
+        <v>116</v>
+      </c>
+      <c r="C37">
         <v>-53.658145904541</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>34.5166625976562</v>
       </c>
-      <c r="D37" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37">
+        <v>53.658145904541</v>
+      </c>
+      <c r="F37">
+        <v>-32.8149874210358</v>
+      </c>
+      <c r="G37">
+        <v>39</v>
+      </c>
+      <c r="H37">
+        <v>44</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38">
+      <c r="B38" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38">
         <v>-213.341857910156</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>-47.1166648864746</v>
       </c>
-      <c r="D38" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38">
+        <v>213.341857910156</v>
+      </c>
+      <c r="F38">
+        <v>87.852180480957</v>
+      </c>
+      <c r="G38">
+        <v>39</v>
+      </c>
+      <c r="H38">
+        <v>45</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39">
+      <c r="B39" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39">
         <v>-473.425201416016</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>16.8478012084961</v>
       </c>
-      <c r="D39" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39">
+        <v>487.715170860291</v>
+      </c>
+      <c r="F39">
+        <v>183.211753845215</v>
+      </c>
+      <c r="G39">
+        <v>40</v>
+      </c>
+      <c r="H39">
+        <v>41</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B40">
+      <c r="B40" t="s">
+        <v>119</v>
+      </c>
+      <c r="C40">
         <v>407.795196533203</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>-40.377799987793</v>
       </c>
-      <c r="D40" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="E40">
+        <v>-404.72912812233</v>
+      </c>
+      <c r="F40">
+        <v>74.104549407959</v>
+      </c>
+      <c r="G40">
+        <v>40</v>
+      </c>
+      <c r="H40">
+        <v>48</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="B41">
+      <c r="B41" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41">
         <v>297.284851074219</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>-104.429664611816</v>
       </c>
-      <c r="D41" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="E41">
+        <v>-293.744661569595</v>
+      </c>
+      <c r="F41">
+        <v>157.532508850098</v>
+      </c>
+      <c r="G41">
+        <v>41</v>
+      </c>
+      <c r="H41">
+        <v>42</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="B42">
+      <c r="B42" t="s">
+        <v>121</v>
+      </c>
+      <c r="C42">
         <v>108.597091674805</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>-97.7925338745117</v>
       </c>
-      <c r="D42" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="E42">
+        <v>-108.574694568291</v>
+      </c>
+      <c r="F42">
+        <v>98.0389020591974</v>
+      </c>
+      <c r="G42">
+        <v>43</v>
+      </c>
+      <c r="H42">
+        <v>44</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="B43">
+      <c r="B43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43">
         <v>-212.633438110352</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>-70.0639114379883</v>
       </c>
-      <c r="D43" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+      <c r="E43">
+        <v>213.944865226746</v>
+      </c>
+      <c r="F43">
+        <v>108.357582092285</v>
+      </c>
+      <c r="G43">
+        <v>44</v>
+      </c>
+      <c r="H43">
+        <v>45</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="B44">
+      <c r="B44" t="s">
+        <v>123</v>
+      </c>
+      <c r="C44">
         <v>-389.217224121094</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>-180.091598510742</v>
       </c>
-      <c r="D44" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+      <c r="E44">
+        <v>389.842050433159</v>
+      </c>
+      <c r="F44">
+        <v>196.49328994751</v>
+      </c>
+      <c r="G44">
+        <v>45</v>
+      </c>
+      <c r="H44">
+        <v>51</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B45">
+      <c r="B45" t="s">
+        <v>124</v>
+      </c>
+      <c r="C45">
         <v>-45.1817512512207</v>
       </c>
-      <c r="C45">
+      <c r="D45">
         <v>-21.9133739471436</v>
       </c>
-      <c r="D45" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+      <c r="E45">
+        <v>45.2205991186202</v>
+      </c>
+      <c r="F45">
+        <v>22.5047248601913</v>
+      </c>
+      <c r="G45">
+        <v>46</v>
+      </c>
+      <c r="H45">
+        <v>49</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="B46">
+      <c r="B46" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46">
         <v>-163.088302612305</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>-141.378189086914</v>
       </c>
-      <c r="D46" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="E46">
+        <v>163.529133737087</v>
+      </c>
+      <c r="F46">
+        <v>146.103898525238</v>
+      </c>
+      <c r="G46">
+        <v>47</v>
+      </c>
+      <c r="H46">
+        <v>48</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>45</v>
       </c>
-      <c r="B47">
+      <c r="B47" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47">
         <v>-40.0316848754883</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>108.788177490234</v>
       </c>
-      <c r="D47" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+      <c r="E47">
+        <v>40.4432264566422</v>
+      </c>
+      <c r="F47">
+        <v>-102.836652755737</v>
+      </c>
+      <c r="G47">
+        <v>47</v>
+      </c>
+      <c r="H47">
+        <v>53</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="B48">
+      <c r="B48" t="s">
+        <v>127</v>
+      </c>
+      <c r="C48">
         <v>731.122192382812</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>-83.2284240722656</v>
       </c>
-      <c r="D48" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+      <c r="E48">
+        <v>-726.842031478882</v>
+      </c>
+      <c r="F48">
+        <v>188.330154418945</v>
+      </c>
+      <c r="G48">
+        <v>50</v>
+      </c>
+      <c r="H48">
+        <v>51</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="1">
         <v>47</v>
       </c>
-      <c r="B49">
+      <c r="B49" t="s">
+        <v>128</v>
+      </c>
+      <c r="C49">
         <v>44.2680015563965</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>-31.7709140777588</v>
       </c>
-      <c r="D49" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+      <c r="E49">
+        <v>-44.2384835314006</v>
+      </c>
+      <c r="F49">
+        <v>32.1278137862682</v>
+      </c>
+      <c r="G49">
+        <v>52</v>
+      </c>
+      <c r="H49">
+        <v>55</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="1">
         <v>48</v>
       </c>
-      <c r="B50">
+      <c r="B50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50">
         <v>-300.699340820312</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>12.8163728713989</v>
       </c>
-      <c r="D50" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+      <c r="E50">
+        <v>304.031141281128</v>
+      </c>
+      <c r="F50">
+        <v>26.3084783554077</v>
+      </c>
+      <c r="G50">
+        <v>53</v>
+      </c>
+      <c r="H50">
+        <v>54</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="1">
         <v>49</v>
       </c>
-      <c r="B51">
+      <c r="B51" t="s">
+        <v>130</v>
+      </c>
+      <c r="C51">
         <v>198.104705810547</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>159.805221557617</v>
       </c>
-      <c r="D51" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="E51">
+        <v>-197.182415127754</v>
+      </c>
+      <c r="F51">
+        <v>-149.09245967865</v>
+      </c>
+      <c r="G51">
+        <v>54</v>
+      </c>
+      <c r="H51">
+        <v>55</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="1">
         <v>50</v>
       </c>
-      <c r="B52">
+      <c r="B52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C52">
         <v>-80.5791168212891</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>158.773574829102</v>
       </c>
-      <c r="D52" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+      <c r="E52">
+        <v>81.0761565566063</v>
+      </c>
+      <c r="F52">
+        <v>-150.629770278931</v>
+      </c>
+      <c r="G52">
+        <v>55</v>
+      </c>
+      <c r="H52">
+        <v>56</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="1">
         <v>51</v>
       </c>
-      <c r="B53">
+      <c r="B53" t="s">
+        <v>132</v>
+      </c>
+      <c r="C53">
         <v>-80.1621246337891</v>
       </c>
-      <c r="C53">
+      <c r="D53">
         <v>76.4912796020508</v>
       </c>
-      <c r="D53" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+      <c r="E53">
+        <v>80.2864679098129</v>
+      </c>
+      <c r="F53">
+        <v>-74.5017871856689</v>
+      </c>
+      <c r="G53">
+        <v>56</v>
+      </c>
+      <c r="H53">
+        <v>57</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="1">
         <v>52</v>
       </c>
-      <c r="B54">
+      <c r="B54" t="s">
+        <v>133</v>
+      </c>
+      <c r="C54">
         <v>-200.914031982422</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>20.0663280487061</v>
       </c>
-      <c r="D54" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
+      <c r="E54">
+        <v>201.301208794117</v>
+      </c>
+      <c r="F54">
+        <v>-13.8231010437012</v>
+      </c>
+      <c r="G54">
+        <v>56</v>
+      </c>
+      <c r="H54">
+        <v>66</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="1">
         <v>53</v>
       </c>
-      <c r="B55">
+      <c r="B55" t="s">
+        <v>134</v>
+      </c>
+      <c r="C55">
         <v>-444.215026855469</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>76.2422256469727</v>
       </c>
-      <c r="D55" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
+      <c r="E55">
+        <v>444.706102818251</v>
+      </c>
+      <c r="F55">
+        <v>-69.8582382202148</v>
+      </c>
+      <c r="G55">
+        <v>57</v>
+      </c>
+      <c r="H55">
+        <v>58</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="1">
         <v>54</v>
       </c>
-      <c r="B56">
+      <c r="B56" t="s">
+        <v>135</v>
+      </c>
+      <c r="C56">
         <v>363.928527832031</v>
       </c>
-      <c r="C56">
+      <c r="D56">
         <v>9.50827312469482</v>
       </c>
-      <c r="D56" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
+      <c r="E56">
+        <v>-362.647222280502</v>
+      </c>
+      <c r="F56">
+        <v>8.43000316619873</v>
+      </c>
+      <c r="G56">
+        <v>57</v>
+      </c>
+      <c r="H56">
+        <v>60</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="1">
         <v>55</v>
       </c>
-      <c r="B57">
+      <c r="B57" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57">
         <v>455.357727050781</v>
       </c>
-      <c r="C57">
+      <c r="D57">
         <v>29.3667526245117</v>
       </c>
-      <c r="D57" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
+      <c r="E57">
+        <v>-453.843757748604</v>
+      </c>
+      <c r="F57">
+        <v>-6.15255928039551</v>
+      </c>
+      <c r="G57">
+        <v>58</v>
+      </c>
+      <c r="H57">
+        <v>59</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="1">
         <v>56</v>
       </c>
-      <c r="B58">
+      <c r="B58" t="s">
+        <v>137</v>
+      </c>
+      <c r="C58">
         <v>-355.063873291016</v>
       </c>
-      <c r="C58">
+      <c r="D58">
         <v>24.1102695465088</v>
       </c>
-      <c r="D58" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
+      <c r="E58">
+        <v>356.139372706413</v>
+      </c>
+      <c r="F58">
+        <v>-11.5115613937378</v>
+      </c>
+      <c r="G58">
+        <v>58</v>
+      </c>
+      <c r="H58">
+        <v>63</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="1">
         <v>57</v>
       </c>
-      <c r="B59">
+      <c r="B59" t="s">
+        <v>138</v>
+      </c>
+      <c r="C59">
         <v>219.843795776367</v>
       </c>
-      <c r="C59">
+      <c r="D59">
         <v>-68.5639266967773</v>
       </c>
-      <c r="D59" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
+      <c r="E59">
+        <v>-219.586164563894</v>
+      </c>
+      <c r="F59">
+        <v>71.5266857147217</v>
+      </c>
+      <c r="G59">
+        <v>59</v>
+      </c>
+      <c r="H59">
+        <v>60</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="1">
         <v>58</v>
       </c>
-      <c r="B60">
+      <c r="B60" t="s">
+        <v>139</v>
+      </c>
+      <c r="C60">
         <v>373.433410644531</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>-132.194732666016</v>
       </c>
-      <c r="D60" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
+      <c r="E60">
+        <v>-369.146777153015</v>
+      </c>
+      <c r="F60">
+        <v>199.848991394043</v>
+      </c>
+      <c r="G60">
+        <v>60</v>
+      </c>
+      <c r="H60">
+        <v>61</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>59</v>
       </c>
-      <c r="B61">
+      <c r="B61" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61">
         <v>358.520782470703</v>
       </c>
-      <c r="C61">
+      <c r="D61">
         <v>19.9688873291016</v>
       </c>
-      <c r="D61" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
+      <c r="E61">
+        <v>-357.900282263756</v>
+      </c>
+      <c r="F61">
+        <v>-13.2985100746155</v>
+      </c>
+      <c r="G61">
+        <v>62</v>
+      </c>
+      <c r="H61">
+        <v>63</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="1">
         <v>60</v>
       </c>
-      <c r="B62">
+      <c r="B62" t="s">
+        <v>141</v>
+      </c>
+      <c r="C62">
         <v>291.479217529297</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>-40.8519592285156</v>
       </c>
-      <c r="D62" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
+      <c r="E62">
+        <v>-291.06388604641</v>
+      </c>
+      <c r="F62">
+        <v>45.3167729377747</v>
+      </c>
+      <c r="G62">
+        <v>62</v>
+      </c>
+      <c r="H62">
+        <v>65</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="1">
         <v>61</v>
       </c>
-      <c r="B63">
+      <c r="B63" t="s">
+        <v>142</v>
+      </c>
+      <c r="C63">
         <v>283.734710693359</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <v>-87.3529205322266</v>
       </c>
-      <c r="D63" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
+      <c r="E63">
+        <v>-282.7955981493</v>
+      </c>
+      <c r="F63">
+        <v>97.8918495178223</v>
+      </c>
+      <c r="G63">
+        <v>65</v>
+      </c>
+      <c r="H63">
+        <v>66</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" s="1">
         <v>62</v>
       </c>
-      <c r="B64">
+      <c r="B64" t="s">
+        <v>143</v>
+      </c>
+      <c r="C64">
         <v>81.4943771362305</v>
       </c>
-      <c r="C64">
+      <c r="D64">
         <v>-57.9088554382324</v>
       </c>
-      <c r="D64" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
+      <c r="E64">
+        <v>-81.3145986646414</v>
+      </c>
+      <c r="F64">
+        <v>60.0761847496033</v>
+      </c>
+      <c r="G64">
+        <v>66</v>
+      </c>
+      <c r="H64">
+        <v>67</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" s="1">
         <v>63</v>
       </c>
-      <c r="B65">
+      <c r="B65" t="s">
+        <v>144</v>
+      </c>
+      <c r="C65">
         <v>-238.685394287109</v>
       </c>
-      <c r="C65">
+      <c r="D65">
         <v>-181.846542358398</v>
       </c>
-      <c r="D65" t="s">
-        <v>138</v>
+      <c r="E65">
+        <v>239.598876357079</v>
+      </c>
+      <c r="F65">
+        <v>191.387354850769</v>
+      </c>
+      <c r="G65">
+        <v>67</v>
+      </c>
+      <c r="H65">
+        <v>68</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3151,284 +4351,584 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>75</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2">
         <v>250</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>196.003524780273</v>
       </c>
-      <c r="D2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>-250</v>
+      </c>
+      <c r="F2">
+        <v>-178.429967880249</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>54</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3">
         <v>545</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>70.0102157592773</v>
       </c>
-      <c r="D3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>-545</v>
+      </c>
+      <c r="F3">
+        <v>19.9719696044922</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>58</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4">
         <v>650</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>80.7825469970703</v>
       </c>
-      <c r="D4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>-650</v>
+      </c>
+      <c r="F4">
+        <v>20.8830413818359</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>62</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5">
         <v>632</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0.268114477396011</v>
       </c>
-      <c r="D5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>-628.779601573944</v>
+      </c>
+      <c r="F5">
+        <v>65.0599723756313</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>19</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6">
         <v>505.000030517578</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>116.574073791504</v>
       </c>
-      <c r="D6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>-502.592056035995</v>
+      </c>
+      <c r="F6">
+        <v>-68.4145889282227</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7">
         <v>700</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>254.488632202148</v>
       </c>
-      <c r="D7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7">
+        <v>-700</v>
+      </c>
+      <c r="F7">
+        <v>-178.890022277832</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
+        <v>22</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8">
         <v>540</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>49.074535369873</v>
       </c>
-      <c r="D8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8">
+        <v>-538.253034949303</v>
+      </c>
+      <c r="F8">
+        <v>18.4747734069824</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9">
         <v>800</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>59.8070030212402</v>
       </c>
-      <c r="D9" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9">
+        <v>-794.85138463974</v>
+      </c>
+      <c r="F9">
+        <v>40.590991973877</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>29</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10">
         <v>500</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-13.1040992736816</v>
       </c>
-      <c r="D10" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10">
+        <v>-500</v>
+      </c>
+      <c r="F10">
+        <v>82.0701789855957</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <v>31</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11">
         <v>1000</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>8.32247352600098</v>
       </c>
-      <c r="D11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11">
+        <v>-1000</v>
+      </c>
+      <c r="F11">
+        <v>132.295278549194</v>
+      </c>
+      <c r="G11">
+        <v>11</v>
+      </c>
+      <c r="H11">
+        <v>32</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12">
         <v>1350</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>280.056823730469</v>
       </c>
-      <c r="D12" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12">
+        <v>-1350</v>
+      </c>
+      <c r="F12">
+        <v>-130.554107666016</v>
+      </c>
+      <c r="G12">
+        <v>12</v>
+      </c>
+      <c r="H12">
+        <v>36</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C13">
         <v>3591</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>885.036254882812</v>
       </c>
-      <c r="D13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13">
+        <v>-3591</v>
+      </c>
+      <c r="F13">
+        <v>-407.376037597656</v>
+      </c>
+      <c r="G13">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>17</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14">
         <v>1785</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>47.4829330444336</v>
       </c>
-      <c r="D14" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14">
+        <v>-1785</v>
+      </c>
+      <c r="F14">
+        <v>0.344257354736328</v>
+      </c>
+      <c r="G14">
+        <v>14</v>
+      </c>
+      <c r="H14">
+        <v>41</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15">
         <v>1000</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>76.7277374267578</v>
       </c>
-      <c r="D15" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15">
+        <v>-1000</v>
+      </c>
+      <c r="F15">
+        <v>-61.6394309997559</v>
+      </c>
+      <c r="G15">
+        <v>15</v>
+      </c>
+      <c r="H15">
+        <v>42</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16">
         <v>3379.53173828125</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>93.6414337158203</v>
       </c>
-      <c r="D16" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16">
+        <v>-3379.53173828125</v>
+      </c>
+      <c r="F16">
+        <v>249.258682250977</v>
+      </c>
+      <c r="G16">
+        <v>16</v>
+      </c>
+      <c r="H16">
+        <v>18</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17">
         <v>177.675216674805</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>39.8539962768555</v>
       </c>
-      <c r="D17" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17">
+        <v>-177.408001869917</v>
+      </c>
+      <c r="F17">
+        <v>-34.5860471725464</v>
+      </c>
+      <c r="G17">
+        <v>19</v>
+      </c>
+      <c r="H17">
+        <v>20</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18">
         <v>246.531799316406</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>-99.9015426635742</v>
       </c>
-      <c r="D18" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18">
+        <v>-246.465869940817</v>
+      </c>
+      <c r="F18">
+        <v>104.780316352844</v>
+      </c>
+      <c r="G18">
+        <v>34</v>
+      </c>
+      <c r="H18">
+        <v>35</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19">
         <v>1.76092517375946</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>42.3444747924805</v>
       </c>
-      <c r="D19" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19">
+        <v>-1.72190135344863</v>
+      </c>
+      <c r="F19">
+        <v>-41.2835147380829</v>
+      </c>
+      <c r="G19">
+        <v>63</v>
+      </c>
+      <c r="H19">
+        <v>64</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="s">
+        <v>163</v>
+      </c>
+      <c r="C20">
         <v>-7.27809762954712</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>-46.7164688110352</v>
       </c>
-      <c r="D20" t="s">
-        <v>157</v>
+      <c r="E20">
+        <v>7.32919239997864</v>
+      </c>
+      <c r="F20">
+        <v>48.1056079864502</v>
+      </c>
+      <c r="G20">
+        <v>64</v>
+      </c>
+      <c r="H20">
+        <v>65</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
